--- a/templates/oefen/oefen_opdracht_template_full.xlsx
+++ b/templates/oefen/oefen_opdracht_template_full.xlsx
@@ -5720,19 +5720,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:38.903460</t>
+    <t>2026-05-19 11:29:12.916944</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>

--- a/templates/oefen/oefen_opdracht_template_full.xlsx
+++ b/templates/oefen/oefen_opdracht_template_full.xlsx
@@ -5720,13 +5720,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:29:12.916944</t>
+    <t>2026-05-19 14:53:03.634801</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
